--- a/backend/aes_ga_history.xlsx
+++ b/backend/aes_ga_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -435,6 +435,8 @@
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,6 +532,16 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>ber_value</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ber_percentage</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>catatan</t>
         </is>
       </c>
@@ -537,7 +549,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-07 17:39:50</t>
+          <t>2026-05-11 05:01:51</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -547,19 +559,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PDF_Deid_Deidentification_0.pdf</t>
+          <t>PDF_Deid_Deidentification_2.pdf</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>38.48</v>
+        <v>38.14</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16EBB9E26595057C8C8530D8EF7C3E0A</t>
+          <t>2BCE6CBBF98CE6145F33E8874550BE19</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.8772</v>
+        <v>0.7312</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -598,22 +610,32 @@
         <v>30</v>
       </c>
       <c r="O2" t="n">
-        <v>495</v>
+        <v>540</v>
       </c>
       <c r="P2" t="n">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.953897</v>
+        <v>0.950953</v>
       </c>
       <c r="R2" t="n">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-07 17:40:16</t>
+          <t>2026-05-11 05:02:24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -623,49 +645,45 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PDF_Deid_Deidentification_0.pdf</t>
+          <t>PDF_Deid_Deidentification_2.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28.80</t>
+          <t>28.54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16EBB9E26595057C8C8530D8EF7C3E0A</t>
+          <t>2BCE6CBBF98CE6145F33E8874550BE19</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.8772</v>
+        <v>0.7312</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.4231</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7.99485109660187</v>
+        <v>7.995557407220004</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lolos</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Lolos</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.06543186399007618</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5235742723025523</v>
       </c>
       <c r="M3" t="n">
         <v>60</v>
@@ -674,18 +692,1404 @@
         <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>495</v>
+        <v>540</v>
       </c>
       <c r="P3" t="n">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.953897</v>
+        <v>0.950953</v>
       </c>
       <c r="R3" t="n">
-        <v>33</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.499120</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>49.9120%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-14 16:19:30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PDF_Deid_Deidentification_0.pdf</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>90ACA1113A2C0FA7BF83A75AF3E99B3D</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9036999999999999</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>60</v>
+      </c>
+      <c r="N4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O4" t="n">
+        <v>15</v>
+      </c>
+      <c r="P4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.952732</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:30:52</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Data_Uji_2.pdf</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>6733DD4A825E882801056435CD7DA747</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>60</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O5" t="n">
+        <v>720</v>
+      </c>
+      <c r="P5" t="n">
+        <v>540</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.956335</v>
+      </c>
+      <c r="R5" t="n">
+        <v>48</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:31:21</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Data_Uji_3.pdf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0E20D77154EE0DB3A254D9131647E227</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>60</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30</v>
+      </c>
+      <c r="O6" t="n">
+        <v>525</v>
+      </c>
+      <c r="P6" t="n">
+        <v>395</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.950806</v>
+      </c>
+      <c r="R6" t="n">
+        <v>35</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:31:42</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Data_Uji_5.pdf</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>07D26879FB6139FABA3F969CE7C1B16F</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6038</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>60</v>
+      </c>
+      <c r="N7" t="n">
+        <v>30</v>
+      </c>
+      <c r="O7" t="n">
+        <v>375</v>
+      </c>
+      <c r="P7" t="n">
+        <v>264</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.950499</v>
+      </c>
+      <c r="R7" t="n">
+        <v>25</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:31:46</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Data_Uji_1.pdf</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>63811665A42F1AACE4377F41AABCBF13</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>60</v>
+      </c>
+      <c r="N8" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" t="n">
+        <v>75</v>
+      </c>
+      <c r="P8" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.9532620000000001</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:32:57</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Data_Uji_4.pdf</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7C9D6206578DAA5A652077AEE1D12F42</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>60</v>
+      </c>
+      <c r="N9" t="n">
+        <v>30</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1380</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1122</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.951946</v>
+      </c>
+      <c r="R9" t="n">
+        <v>42</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:32:59</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Data_Uji_4_Sedang.pdf</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>249.82</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0659CEBC172C14F8929D789145F6B9E5</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.4399</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>60</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" t="n">
+        <v>15</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.963265</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:33:02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Data_Uji_5_Sedang.pdf</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>250.35</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9342EECFF97F340A4FAACD2FBABF1A70</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.1353</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N11" t="n">
+        <v>30</v>
+      </c>
+      <c r="O11" t="n">
+        <v>15</v>
+      </c>
+      <c r="P11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.961637</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:33:05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Data_Uji_2_Sedang.pdf</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>258.49</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>446D425C265CC39AC1101F1CF9134CAD</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.7376</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>60</v>
+      </c>
+      <c r="N12" t="n">
+        <v>30</v>
+      </c>
+      <c r="O12" t="n">
+        <v>15</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.957792</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:33:07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Data_Uji_3_Sedang.pdf</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>260.82</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CACA9556D3C5A814317D7B159910C92E</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.9099</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>60</v>
+      </c>
+      <c r="N13" t="n">
+        <v>30</v>
+      </c>
+      <c r="O13" t="n">
+        <v>15</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.958687</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:33:10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Data_Uji_1_Sedang.pdf</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>266.73</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>23B5F511C6E2B51C88A701E10EF69D1A</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.9581</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>60</v>
+      </c>
+      <c r="N14" t="n">
+        <v>30</v>
+      </c>
+      <c r="O14" t="n">
+        <v>15</v>
+      </c>
+      <c r="P14" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.961239</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:33:14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Data_Uji_Besar.pdf</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>612.33</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5E0CB414ECEED19D497320F8FE9C77E3</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>9.7461</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>60</v>
+      </c>
+      <c r="N15" t="n">
+        <v>30</v>
+      </c>
+      <c r="O15" t="n">
+        <v>15</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.950693</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-16 08:10:38</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Kesehatan_1.docx</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FEA1D0545497B170B23EC66AA859C11E</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
+      <c r="N16" t="n">
+        <v>30</v>
+      </c>
+      <c r="O16" t="n">
+        <v>720</v>
+      </c>
+      <c r="P16" t="n">
+        <v>635</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.954473</v>
+      </c>
+      <c r="R16" t="n">
+        <v>48</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-16 08:10:39</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Kesehatan_2.docx</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>73.03</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8C79C6E33792B20B5C48FFB4CE4C58BE</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7544</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
+      <c r="N17" t="n">
+        <v>30</v>
+      </c>
+      <c r="O17" t="n">
+        <v>15</v>
+      </c>
+      <c r="P17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.958575</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-16 08:10:40</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Kesehatan_3.docx</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ADCD323D0102A9C6AF2410ECC2811B8E</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>60</v>
+      </c>
+      <c r="N18" t="n">
+        <v>30</v>
+      </c>
+      <c r="O18" t="n">
+        <v>15</v>
+      </c>
+      <c r="P18" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.954001</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-16 08:10:42</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AES-128-GA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kesehatan.docx</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>21F9B9E40DFE98654B0F1F5FCDA42F55</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6429</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
+      <c r="N19" t="n">
+        <v>30</v>
+      </c>
+      <c r="O19" t="n">
+        <v>15</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.957132</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
